--- a/backend/elderlycare-common/src/main/resources/excel_model/NursingLevel.xlsx
+++ b/backend/elderlycare-common/src/main/resources/excel_model/NursingLevel.xlsx
@@ -445,13 +445,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,11 +469,6 @@
           <t>费用</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -492,11 +486,6 @@
           <t>fee</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>operation</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -512,11 +501,6 @@
       <c r="C3" s="3" t="n">
         <v>3200</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>编辑</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -532,11 +516,6 @@
       <c r="C4" s="3" t="n">
         <v>2200</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>编辑</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -551,11 +530,6 @@
       </c>
       <c r="C5" s="3" t="n">
         <v>1000</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>编辑</t>
-        </is>
       </c>
     </row>
   </sheetData>
